--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.31772277746074</v>
+        <v>2.001629951337371</v>
       </c>
       <c r="D2" t="n">
-        <v>12.92357889085323</v>
+        <v>2.10008156976365</v>
       </c>
       <c r="E2" t="n">
-        <v>12.01366587023479</v>
+        <v>1.952220703913154</v>
       </c>
       <c r="F2" t="n">
-        <v>9.754037814234165</v>
+        <v>1.585031144813052</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.125342126129844</v>
+        <v>1.3203680954961</v>
       </c>
       <c r="D3" t="n">
-        <v>9.38481875681985</v>
+        <v>1.525033047983226</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01366587023479</v>
+        <v>1.952220703913154</v>
       </c>
       <c r="F3" t="n">
-        <v>9.754037814234165</v>
+        <v>1.585031144813052</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.13348042684993</v>
+        <v>3.596690569363114</v>
       </c>
       <c r="D4" t="n">
-        <v>21.44109163465497</v>
+        <v>3.484177390631433</v>
       </c>
       <c r="E4" t="n">
-        <v>12.01366587023479</v>
+        <v>1.952220703913154</v>
       </c>
       <c r="F4" t="n">
-        <v>9.754037814234165</v>
+        <v>1.585031144813052</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.11915976897676</v>
+        <v>4.406863462458724</v>
       </c>
       <c r="D5" t="n">
-        <v>27.31607678120283</v>
+        <v>4.438862476945461</v>
       </c>
       <c r="E5" t="n">
-        <v>12.01366587023479</v>
+        <v>1.952220703913154</v>
       </c>
       <c r="F5" t="n">
-        <v>9.754037814234165</v>
+        <v>1.585031144813052</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.29697663145448</v>
+        <v>6.710758702611352</v>
       </c>
       <c r="D6" t="n">
-        <v>21.9930047394507</v>
+        <v>3.573863270160739</v>
       </c>
       <c r="E6" t="n">
-        <v>12.01366587023479</v>
+        <v>1.952220703913154</v>
       </c>
       <c r="F6" t="n">
-        <v>9.754037814234165</v>
+        <v>1.585031144813052</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.69004204831579</v>
+        <v>2.387131832851316</v>
       </c>
       <c r="D7" t="n">
-        <v>14.23048897338631</v>
+        <v>2.312454458175276</v>
       </c>
       <c r="E7" t="n">
-        <v>12.01366587023479</v>
+        <v>1.952220703913154</v>
       </c>
       <c r="F7" t="n">
-        <v>9.754037814234165</v>
+        <v>1.585031144813052</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.01443471739265</v>
+        <v>5.527345641576305</v>
       </c>
       <c r="D8" t="n">
-        <v>34.95928067429757</v>
+        <v>5.680883109573356</v>
       </c>
       <c r="E8" t="n">
-        <v>12.01366587023479</v>
+        <v>1.952220703913154</v>
       </c>
       <c r="F8" t="n">
-        <v>9.754037814234165</v>
+        <v>1.585031144813052</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.366233880826765</v>
+        <v>0.2220130056343493</v>
       </c>
       <c r="D9" t="n">
-        <v>0.783714809830841</v>
+        <v>0.1273536565975117</v>
       </c>
       <c r="E9" t="n">
-        <v>12.01366587023479</v>
+        <v>1.952220703913154</v>
       </c>
       <c r="F9" t="n">
-        <v>9.754037814234165</v>
+        <v>1.585031144813052</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.68972980074787</v>
+        <v>4.012081092621529</v>
       </c>
       <c r="D10" t="n">
-        <v>24.88222590745</v>
+        <v>4.043361709960625</v>
       </c>
       <c r="E10" t="n">
-        <v>12.01366587023479</v>
+        <v>1.952220703913154</v>
       </c>
       <c r="F10" t="n">
-        <v>9.754037814234165</v>
+        <v>1.585031144813052</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
